--- a/daily_matches/job_matches_2026-08-15.xlsx
+++ b/daily_matches/job_matches_2026-08-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hadoop Solutions Developer</t>
+          <t>Agentic AI Engineering Architect (Remote -US)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e611db79889b1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Azure ML, MLflow, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, Python</t>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986170411aab2db0</t>
+          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Engineer II, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Azure ML, MLflow, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Git, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33354ecb78e1f09</t>
+          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Terraform, Git, Snowflake, Databricks, PostgreSQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, Azure ML</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
+          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
+          <t>Software Engineer II - AI/ML Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Glue, FastAPI, CI/CD, Git, Snowflake, PySpark, Kafka</t>
+          <t>RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
+          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Engineer, SRE TechOps CICD (Remote)</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, MySQL</t>
+          <t>RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02946a77bdd7bddf</t>
+          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>QA Software Engineer NC Hybrid</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, CI/CD, Git, Databricks, PySpark, Hadoop</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,102 +706,102 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
+          <t>https://www.indeed.com/viewjob?jk=27a49c7a90f5d6c1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Senior Data Engineer (On-Site)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Kinesis, CI/CD, Jenkins, Git, Snowflake, Kafka, PostgreSQL, NoSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
+          <t>https://www.indeed.com/viewjob?jk=d460a6aac4fd260a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Kinesis, CI/CD, Jenkins, Git, Snowflake, Kafka, PostgreSQL, NoSQL, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
+          <t>https://www.indeed.com/viewjob?jk=afe1d38414cdf113</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Law School Admission Council</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Newtown, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Kafka, PostgreSQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Pinecone, Prompt Engineering, CI/CD, Git, Power BI, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,102 +811,102 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
+          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform Infrastructure</t>
+          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SmarterDx</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python</t>
+          <t>RAG, S3, Glue, Data Lake, Terraform, Git, Snowflake, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer, Global</t>
+          <t>SR Azure Data Factory- Remote</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
+          <t>RAG, Synapse, Data Lake, CI/CD, Snowflake, Databricks, PySpark, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8625d99e5c7e4a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Senior Data Scientist (Internal Audit Product Engineering)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, R</t>
+          <t>Data Scientist, RAG, Copilot, Data Lake, AKS, Databricks, PySpark, Hadoop, Power BI, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1e2353d3b351061</t>
+          <t>https://www.indeed.com/viewjob?jk=ea7fec3ec946a315</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, R</t>
+          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891698c73f0a37c8</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, R</t>
+          <t>LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688e0aa6648a4e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=8c31b26146016930</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Senior Machine Learning System Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, R</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Dask, Python, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22deb81a3b468745</t>
+          <t>https://www.indeed.com/viewjob?jk=64e9ffc97152ffed</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Scientist - Lewis Katz School of Medicine</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Temple University Health System</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, TensorFlow, PyTorch, Data Lake, MLflow, Python, SQL</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,19 +1056,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6ca1ba73e5a70de</t>
+          <t>https://www.indeed.com/viewjob?jk=6498d6e41474c2f6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GCP Architect Grade C2</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Lyra Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, Terraform, BigQuery, Python, SQL, R, Scala</t>
+          <t>RAG, EC2, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
+          <t>https://www.indeed.com/viewjob?jk=a4599d6c68fd3447</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ID Software/Application Engineer Professional</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Guardian Staffing Solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, NoSQL, SQL, R</t>
+          <t>RAG, Copilot, Terraform, Git, Snowflake, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d13b1952f96760d4</t>
+          <t>https://www.indeed.com/viewjob?jk=a7021a5784447861</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
+          <t>Software Engineer III - AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>True Zero Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Glue, Athena, Redshift, CI/CD, Terraform, Redshift, Python, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
+          <t>https://www.indeed.com/viewjob?jk=9b4a8e4b1783d435</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Research Informatics</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mammoth Biosciences</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, AKS, CI/CD, Terraform, Git, Python, SQL</t>
+          <t>Generative AI, LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
+          <t>https://www.indeed.com/viewjob?jk=4de0e209dbdff175</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>Generative AI, LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce7678e2aaec62f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer (Remote)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, Terraform, Kafka, Cassandra, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088f48987b0ed427</t>
+          <t>https://www.indeed.com/viewjob?jk=70ff1ca77e90c8f7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Engineer, SDET - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Junior AI Engineer (Pittsburgh, PA)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Wavestone</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=021b25e1008c44c5</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4774f0465c2a99</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>UI Automation - Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,24 +1326,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, Git, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f5e85681842113b</t>
+          <t>https://www.indeed.com/viewjob?jk=ed8c046f4873e89a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Engineer, Data and AI Governance</t>
+          <t>AI Data Engineer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Glue, Terraform, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ccc3e08fb9a9324</t>
+          <t>https://www.indeed.com/viewjob?jk=591604bb6076dc41</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Solution Engineer</t>
+          <t>2027 Data &amp; AI Program - Summer Internship - Analyst - United States</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,102 +1406,102 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
+          <t>https://www.indeed.com/viewjob?jk=cc58ff723d4322ba</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Backend Senior Software Engineer, Attack and User Emulation Team (AUE)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SimSpace Corporation</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, BigQuery, Apache Airflow, Git, BigQuery, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66436ab015e2c188</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Terraform, Python, R, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, CI/CD, MongoDB, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac6c920d740fbc5</t>
+          <t>https://www.indeed.com/viewjob?jk=b4bcb1ec482fd39c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Scientist II, AI Analytics</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Terraform, Python, R, Optimization</t>
+          <t>Data Scientist, Prompt Engineering, TensorFlow, PyTorch, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2b8f8da3d801914</t>
+          <t>https://www.indeed.com/viewjob?jk=2bc1dd2e9f435331</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (Video Understanding &amp; Segmentation)</t>
+          <t>AI Engineer New</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MaxInsights</t>
+          <t>BPD</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, LLaMA, FAISS, PyTorch, Python, R, Scala</t>
+          <t>AI Engineer, RAG, Prompt Engineering, S3, Snowflake, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d451933a055da986</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba109eaf0a1ff84</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Codal</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Databricks, PySpark, Tableau, Python, SQL, R</t>
+          <t>RAG, BigQuery, Docker, Kubernetes, CI/CD, Git, BigQuery, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
+          <t>https://www.indeed.com/viewjob?jk=29bd106fb2f3ca0f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Engineer II - Automation &amp; Development (Remote)</t>
+          <t>Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Networking for Future, Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, CI/CD, Kafka, Python, SQL, R, Optimization</t>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, Terraform, Git, R, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46cbfbffbad9d2c5</t>
+          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Engineer II - Full Stack / Backend Engineer (Remote)</t>
+          <t>Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>U.S. Renal Care</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, SQL, R</t>
+          <t>RAG, Copilot, Prompt Engineering, Kubernetes, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d77abb857a90754</t>
+          <t>https://www.indeed.com/viewjob?jk=526131f40eee19a9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Solution Architect - Syndigo MDM- GCP</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java</t>
+          <t>Generative AI, RAG, Gemini, BigQuery, Dataflow, Git, BigQuery, R, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52d935ba868ca0a</t>
+          <t>https://www.indeed.com/viewjob?jk=bb539f40614a8b41</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Salesforce Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Upstate Coin &amp; Gold</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=305329cc5449f705</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Solution Architect - Syndigo MDM- GCP</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, BigQuery, Dataflow, Git, BigQuery, R, Scala</t>
+          <t>RAG, Copilot, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ee41567e9575ba</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e62e00fe161106</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Enterprise Applications Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Brattle Group, Inc.</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5efe9ee9d7980b21</t>
+          <t>https://www.indeed.com/viewjob?jk=4373a9ead39e2cb8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Spring 2027 AI Applied Research Internship</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, MLflow, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13c54aa529472e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Enterprise Applications Engineer</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>THE BRATTLE GROUP</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ed5b3643ffc6bc</t>
+          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Satellite Capacity Optimization &amp; Planning</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,227 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer - Satellite Capacity Optimization &amp; Planning</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Viasat</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Carlsbad, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>Machine Learning Engineer, TensorFlow, PyTorch, Athena, BigQuery, BigQuery, SQL, R, Optimization</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fac5364852e101ba</t>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa0323513ab14746</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Systems Design Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d24df63f453e70fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sr Analyst, Statistical Inference and Data Science (IKC)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>DaVita</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Git, Tableau, Python, SQL, R, Bayesian</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3807c3bb10e78a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Solutions Engineer, Google Cloud &amp; Maps Platform</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Sanborn Map Company</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, BigQuery, BigQuery, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe9fb5d5db13b111</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SMTS Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3929b8f141724b3</t>
         </is>
       </c>
     </row>
